--- a/output/compliance_report.xlsx
+++ b/output/compliance_report.xlsx
@@ -34,7 +34,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -48,12 +48,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFCCCC"/>
+        <fgColor rgb="00E6E6FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFB3B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -80,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -94,7 +99,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -462,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -566,47 +574,368 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>All structure and union types shall be complete at the end of a translation unit.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>union DataStore {
+    unsigned int raw;
+    unsigned char bytes[4];
+};
+union DataStore g_store;</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>[NEEDS REVIEW - Confidence: 0.86] The MISRA C 2004 rule 18.1 applies here because the union type 'DataStore' is used in the translation unit to store and retrieve data. The code violates this rule because its declaration is incomplete, lacking the necessary members to fully define the union type. The evidence used to infer this violation is the LLM (Language Model) inference, which detected the use of the union type 'DataStore' in the translation unit without a complete declaration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>data.c</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>&lt;global&gt;</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>18.4</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Unions shall not be used.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>0.90</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>control_flow</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Replace union usage with separate variables or tagged struct</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Union type usage found (unions are prohibited). Variable declared with union type</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>device.c</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>reset_device</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Assembly language shall be encapsulated and isolated.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>control_flow</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Encapsulate assembly in a separate function or use compiler intrinsics</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Assembly language used inline (should be encapsulated). Inline assembly keyword detected (asm/__asm__/__asm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>main.c</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>check_limits</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>The operands of a logical &amp;&amp; or || shall be primary‑expressions.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>control_flow+llm</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Add parentheses: change 'a &amp;&amp; b &gt; c' to 'a &amp;&amp; (b &gt; c)'</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>The rule applies here because the code contains a logical &amp;&amp; expression with operands that are not primary-expressions. The code violates this rule because the operand x &gt; 0 is a comparison expression, which is not a primary-expression as required by the rule. This was determined through LLM inference, specifically by analyzing the structure of the logical &amp;&amp; expression and identifying the non-primary-expression operand x &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>main.c</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>check_limits</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>The operands of logical operators (&amp;&amp;, || and !) should be effectively Boolean.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>advisory</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>int check_limits(int x, int y) {
+        if ((x &gt; 0) &amp;&amp; (y &lt; 100) &amp;&amp; (x != y)) { return 1; }
+        return 0; }</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>[NEEDS REVIEW - Confidence: 0.86] The rule applies here because the code uses logical operators (&amp;&amp;) with operands that are not guaranteed to be Boolean. The code violates this rule because the operands of the logical operator &amp;&amp; are not effectively Boolean, as they are integers (x &gt; 0 and y &lt; 100) rather than Boolean values. This is evident from the LLM inference, which detected the logical expression (x &gt; 0 &amp;&amp; y &lt; 100 &amp;&amp; x != y) as not being effectively Boolean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>shared.h</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>&lt;global&gt;</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Unions shall not be used.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>control_flow</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Replace union with separate variables or use a struct with type tag</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Union declaration found (unions are prohibited). Union type declaration detected</t>
         </is>
       </c>
     </row>
@@ -629,12 +958,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -647,7 +976,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -657,7 +986,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -667,7 +996,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -697,7 +1026,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>33.3</v>
       </c>
     </row>
   </sheetData>
